--- a/Unity/Assets/Config/Excel/Datas/StartConfig/Localhost/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/StartConfig/Localhost/StartSceneConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/icepower/Work/Projects/My/X-ET7/Unity/Assets/Config/Excel/Datas/StartConfig/Localhost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD0D2CA-A610-CC4D-B391-6E6FF7D7CF94}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E31F9CA-11F7-6D42-B381-6785003E6AAE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="12940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
